--- a/weekly_template.xlsx
+++ b/weekly_template.xlsx
@@ -142,7 +142,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -161,8 +161,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF1DE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="71">
+  <borders count="78">
     <border>
       <left/>
       <right/>
@@ -978,6 +983,69 @@
         <color auto="1"/>
       </top>
       <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="medium"/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
@@ -986,7 +1054,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1296,6 +1364,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="13" fillId="4" borderId="35" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="14" fillId="4" borderId="35" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="9" fontId="13" fillId="4" borderId="37" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="13" fillId="4" borderId="68" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1868,106 +1978,111 @@
           <t>당월 실적</t>
         </is>
       </c>
-      <c r="E10" s="112" t="n"/>
-      <c r="F10" s="112" t="n"/>
-      <c r="G10" s="112" t="n"/>
-      <c r="H10" s="112" t="n"/>
-      <c r="I10" s="112" t="n"/>
-      <c r="J10" s="113" t="n"/>
+      <c r="E10" s="167" t="n"/>
+      <c r="F10" s="167" t="n"/>
+      <c r="G10" s="167" t="n"/>
+      <c r="H10" s="167" t="n"/>
+      <c r="I10" s="167" t="n"/>
+      <c r="J10" s="168" t="n"/>
       <c r="K10" s="114" t="inlineStr">
         <is>
           <t>연간누계</t>
         </is>
       </c>
-      <c r="L10" s="112" t="n"/>
-      <c r="M10" s="112" t="n"/>
-      <c r="N10" s="112" t="n"/>
-      <c r="O10" s="112" t="n"/>
-      <c r="P10" s="112" t="n"/>
-      <c r="Q10" s="112" t="n"/>
-      <c r="R10" s="112" t="n"/>
-      <c r="S10" s="115" t="n"/>
-    </row>
-    <row r="11" customFormat="1" s="59">
+      <c r="L10" s="167" t="n"/>
+      <c r="M10" s="167" t="n"/>
+      <c r="N10" s="167" t="n"/>
+      <c r="O10" s="167" t="n"/>
+      <c r="P10" s="167" t="n"/>
+      <c r="Q10" s="167" t="n"/>
+      <c r="R10" s="167" t="n"/>
+      <c r="S10" s="168" t="n"/>
+    </row>
+    <row r="11" ht="27" customFormat="1" customHeight="1" s="59">
       <c r="A11" s="116" t="n"/>
       <c r="B11" s="52" t="n"/>
       <c r="C11" s="53" t="n"/>
-      <c r="D11" s="117" t="inlineStr">
-        <is>
-          <t>25실판가</t>
-        </is>
-      </c>
-      <c r="E11" s="55" t="inlineStr">
+      <c r="D11" s="169" t="inlineStr">
+        <is>
+          <t>25
+실판가</t>
+        </is>
+      </c>
+      <c r="E11" s="170" t="inlineStr">
         <is>
           <t>판가율</t>
         </is>
       </c>
-      <c r="F11" s="118" t="inlineStr">
-        <is>
-          <t>26실판가</t>
-        </is>
-      </c>
-      <c r="G11" s="55" t="inlineStr">
+      <c r="F11" s="171" t="inlineStr">
+        <is>
+          <t>26
+실판가</t>
+        </is>
+      </c>
+      <c r="G11" s="170" t="inlineStr">
         <is>
           <t>증감율</t>
         </is>
       </c>
-      <c r="H11" s="55" t="inlineStr">
+      <c r="H11" s="170" t="inlineStr">
         <is>
           <t>비중</t>
         </is>
       </c>
-      <c r="I11" s="55" t="inlineStr">
+      <c r="I11" s="170" t="inlineStr">
         <is>
           <t>판가율</t>
         </is>
       </c>
-      <c r="J11" s="57" t="inlineStr">
+      <c r="J11" s="172" t="inlineStr">
         <is>
           <t>편차</t>
         </is>
       </c>
-      <c r="K11" s="119" t="inlineStr">
-        <is>
-          <t>25실판가</t>
-        </is>
-      </c>
-      <c r="L11" s="55" t="inlineStr">
+      <c r="K11" s="173" t="inlineStr">
+        <is>
+          <t>25
+실판가</t>
+        </is>
+      </c>
+      <c r="L11" s="170" t="inlineStr">
         <is>
           <t>판가율</t>
         </is>
       </c>
-      <c r="M11" s="52" t="inlineStr">
+      <c r="M11" s="174" t="inlineStr">
         <is>
           <t>사업계획</t>
         </is>
       </c>
-      <c r="N11" s="118" t="inlineStr">
-        <is>
-          <t>26실판가</t>
-        </is>
-      </c>
-      <c r="O11" s="52" t="inlineStr">
+      <c r="N11" s="171" t="inlineStr">
+        <is>
+          <t>26
+실판가</t>
+        </is>
+      </c>
+      <c r="O11" s="174" t="inlineStr">
         <is>
           <t>진도율</t>
         </is>
       </c>
-      <c r="P11" s="55" t="inlineStr">
+      <c r="P11" s="170" t="inlineStr">
         <is>
           <t>증감율</t>
         </is>
       </c>
-      <c r="Q11" s="55" t="inlineStr">
+      <c r="Q11" s="170" t="inlineStr">
         <is>
           <t>비중</t>
         </is>
       </c>
-      <c r="R11" s="55" t="inlineStr">
-        <is>
-          <t>26판가율</t>
-        </is>
-      </c>
-      <c r="S11" s="120" t="inlineStr">
+      <c r="R11" s="175" t="inlineStr">
+        <is>
+          <t>26
+판가율</t>
+        </is>
+      </c>
+      <c r="S11" s="176" t="inlineStr">
         <is>
           <t>편차</t>
         </is>
@@ -2098,7 +2213,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="131" t="n"/>
+      <c r="A14" s="177" t="n"/>
       <c r="B14" s="14" t="inlineStr">
         <is>
           <t>네이버스토어</t>
@@ -2155,7 +2270,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="131" t="n"/>
+      <c r="A15" s="177" t="n"/>
       <c r="B15" s="14" t="inlineStr">
         <is>
           <t>원래직입점</t>
@@ -2212,7 +2327,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="131" t="n"/>
+      <c r="A16" s="177" t="n"/>
       <c r="B16" s="14" t="inlineStr">
         <is>
           <t>웹뜰이관</t>
@@ -2269,7 +2384,7 @@
       </c>
     </row>
     <row r="17" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A17" s="136" t="n"/>
+      <c r="A17" s="178" t="n"/>
       <c r="B17" s="34" t="inlineStr">
         <is>
           <t>웍스바이이관</t>
@@ -2334,64 +2449,64 @@
 별</t>
         </is>
       </c>
-      <c r="B18" s="75" t="inlineStr">
+      <c r="B18" s="179" t="inlineStr">
         <is>
           <t>S/D/L</t>
         </is>
       </c>
-      <c r="C18" s="76" t="inlineStr">
+      <c r="C18" s="180" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="D18" s="142" t="n">
+      <c r="D18" s="181" t="n">
         <v>212371711</v>
       </c>
-      <c r="E18" s="78" t="n">
+      <c r="E18" s="182" t="n">
         <v>0.46</v>
       </c>
-      <c r="F18" s="143" t="n">
+      <c r="F18" s="183" t="n">
         <v>234823732</v>
       </c>
-      <c r="G18" s="80" t="n">
+      <c r="G18" s="184" t="n">
         <v>0.106</v>
       </c>
-      <c r="H18" s="78" t="n">
+      <c r="H18" s="182" t="n">
         <v>0.8</v>
       </c>
-      <c r="I18" s="78" t="n">
+      <c r="I18" s="182" t="n">
         <v>0.396</v>
       </c>
-      <c r="J18" s="81" t="n">
+      <c r="J18" s="185" t="n">
         <v>-0.064</v>
       </c>
-      <c r="K18" s="144" t="n">
+      <c r="K18" s="186" t="n">
         <v>3511122909</v>
       </c>
-      <c r="L18" s="78" t="n">
+      <c r="L18" s="182" t="n">
         <v>0.443</v>
       </c>
-      <c r="M18" s="83" t="n"/>
-      <c r="N18" s="143" t="n">
+      <c r="M18" s="187" t="n"/>
+      <c r="N18" s="183" t="n">
         <v>3628107345</v>
       </c>
-      <c r="O18" s="83" t="n"/>
-      <c r="P18" s="80" t="n">
+      <c r="O18" s="187" t="n"/>
+      <c r="P18" s="184" t="n">
         <v>0.033</v>
       </c>
-      <c r="Q18" s="78" t="n">
+      <c r="Q18" s="182" t="n">
         <v>0.782</v>
       </c>
-      <c r="R18" s="78" t="n">
+      <c r="R18" s="182" t="n">
         <v>0.441</v>
       </c>
-      <c r="S18" s="145" t="n">
+      <c r="S18" s="188" t="n">
         <v>-0.002</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="131" t="n"/>
-      <c r="B19" s="146" t="n"/>
+      <c r="A19" s="177" t="n"/>
+      <c r="B19" s="189" t="n"/>
       <c r="C19" s="15" t="inlineStr">
         <is>
           <t>신상</t>
@@ -2443,8 +2558,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="131" t="n"/>
-      <c r="B20" s="146" t="n"/>
+      <c r="A20" s="177" t="n"/>
+      <c r="B20" s="189" t="n"/>
       <c r="C20" s="15" t="inlineStr">
         <is>
           <t>1년차</t>
@@ -2496,8 +2611,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="131" t="n"/>
-      <c r="B21" s="146" t="n"/>
+      <c r="A21" s="177" t="n"/>
+      <c r="B21" s="189" t="n"/>
       <c r="C21" s="15" t="inlineStr">
         <is>
           <t>2년차</t>
@@ -2549,8 +2664,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="131" t="n"/>
-      <c r="B22" s="147" t="n"/>
+      <c r="A22" s="177" t="n"/>
+      <c r="B22" s="190" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
           <t>3년차</t>
@@ -2602,7 +2717,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="131" t="n"/>
+      <c r="A23" s="177" t="n"/>
       <c r="B23" s="24" t="inlineStr">
         <is>
           <t>A</t>
@@ -2659,7 +2774,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="131" t="n"/>
+      <c r="A24" s="177" t="n"/>
       <c r="B24" s="24" t="n">
         <v>0</v>
       </c>
@@ -2714,7 +2829,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="131" t="n"/>
+      <c r="A25" s="177" t="n"/>
       <c r="B25" s="24" t="inlineStr">
         <is>
           <t>J</t>
@@ -2771,7 +2886,7 @@
       </c>
     </row>
     <row r="26" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A26" s="148" t="n"/>
+      <c r="A26" s="178" t="n"/>
       <c r="B26" s="149" t="inlineStr">
         <is>
           <t>N</t>
